--- a/data_out/country_spreadsheets/Greece.xlsx
+++ b/data_out/country_spreadsheets/Greece.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>294.95</v>
       </c>
+      <c r="X2" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>105.33</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>294.01</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>265.01</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>167.94</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>154.59</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>317.39</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>294.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>295.78</v>
       </c>
+      <c r="X3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>194.36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>77.45999999999999</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>146.63</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>301.75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>295.78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>281.56</v>
       </c>
+      <c r="X4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>262.81</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>298.44</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>101.03</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>288.73</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>281.56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>308.67</v>
       </c>
+      <c r="X5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>309.33</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>294.05</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>308.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>248.7</v>
       </c>
+      <c r="X6" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>187.61</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>238.38</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>185.01</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>144.41</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>261.18</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>248.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>298.62</v>
       </c>
+      <c r="X7" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>273.86</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>290.39</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>273.49</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120.81</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>321.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>298.62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>100.66</v>
       </c>
+      <c r="X8" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>165.54</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>148.18</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>114.92</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>46.81</v>
       </c>
+      <c r="X9" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>128.18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>140.77</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>127.79</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>136.74</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>130.84</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>5.39</v>
       </c>
+      <c r="X10" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>182.42</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>123.23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.39</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>0.62</v>
       </c>
+      <c r="X11" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>217.32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>115.14</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>46.7</v>
       </c>
+      <c r="X12" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>228.89</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>112.43</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>46.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>91.84999999999999</v>
       </c>
+      <c r="X13" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>162.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>101.93</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>182.49</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>131.92</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>166.22</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>91.84999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>257.49</v>
       </c>
+      <c r="X14" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>325.92</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>257.49</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>241.08</v>
       </c>
+      <c r="X15" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>236.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>157.37</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>285.78</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>279.21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>262.53</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>241.08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>245.19</v>
       </c>
+      <c r="X16" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>163.64</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>283.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>249.23</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>286.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>245.19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>192.87</v>
       </c>
+      <c r="X17" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>130.28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>111.04</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>261.01</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>203.52</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>275.72</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>192.87</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>246.01</v>
       </c>
+      <c r="X18" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>182.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>108.32</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>118.27</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>194.58</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>249.96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>246.01</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>183.26</v>
       </c>
+      <c r="X19" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>153.58</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>324.92</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>183.26</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>249.01</v>
       </c>
+      <c r="X20" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>161.57</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>235.47</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>116.16</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>223.16</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>288.55</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>249.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>182.87</v>
       </c>
+      <c r="X21" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>272.83</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>228.16</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>331.37</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>182.87</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>112.19</v>
       </c>
+      <c r="X22" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>202.68</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>242.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>284.92</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>112.19</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>83.98999999999999</v>
       </c>
+      <c r="X23" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>198.15</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>195.24</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>158.12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>109.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>171.59</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>110.57</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>302.88</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>83.98999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>44.34</v>
       </c>
+      <c r="X24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>205.89</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>205.69</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>113.09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>196.24</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>111.77</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>226.06</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>110.22</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>133.62</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>302.19</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>44.34</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>56.71</v>
       </c>
+      <c r="X25" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>152.79</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>202.39</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>120.56</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>130.62</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>172.68</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>300.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>56.71</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>235.22</v>
       </c>
+      <c r="X26" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>148.16</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>133.17</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>236.02</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>77.94</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>286.63</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>208.55</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>162.74</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>231.68</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>235.22</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>60.81</v>
       </c>
+      <c r="X27" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>231.79</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>186.34</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>108.18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>289.16</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>223.63</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>60.81</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>155.52</v>
       </c>
+      <c r="X28" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>105.09</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>237.19</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>176.21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>143.22</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>155.52</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>44.16</v>
       </c>
+      <c r="X29" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>216.19</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>178.07</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>204.76</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>102.57</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>263.59</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>44.16</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>122.5</v>
       </c>
+      <c r="X30" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>143.41</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>121.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>114.01</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>162.72</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>192.66</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>122.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>118.31</v>
       </c>
+      <c r="X31" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>118.31</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>219.12</v>
       </c>
+      <c r="X32" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>158.92</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>117.94</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>273.65</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>219.12</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>215.21</v>
       </c>
+      <c r="X33" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>263.97</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>157.78</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>121.94</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>124.17</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>215.21</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>213.92</v>
       </c>
+      <c r="X34" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>309.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>233.59</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>188</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>188.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>173.38</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>277.19</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>213.92</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>212.9</v>
       </c>
+      <c r="X35" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>149.96</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>192.46</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>184.34</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>152.99</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>212.9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>134.73</v>
       </c>
+      <c r="X36" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>137.15</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>134.73</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>35.21</v>
       </c>
+      <c r="X37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>115.17</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>46.43</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>35.21</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>140.91</v>
       </c>
+      <c r="X38" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>77.91</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>104.74</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>140.91</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>25.32</v>
       </c>
+      <c r="X39" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>134.07</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>176.33</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>25.32</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>13.58</v>
       </c>
+      <c r="X40" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>158.86</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>115.48</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>142.68</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>13.58</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3624,6 +5698,57 @@
       <c r="W41" t="n">
         <v>35.19</v>
       </c>
+      <c r="X41" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>39.12</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>159.02</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>147.06</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>88.69</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>196.96</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>35.19</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3701,6 +5826,57 @@
       <c r="W42" t="n">
         <v>46.38</v>
       </c>
+      <c r="X42" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>218.89</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>126.35</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>109.11</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>248.34</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>46.38</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3778,6 +5954,57 @@
       <c r="W43" t="n">
         <v>154.39</v>
       </c>
+      <c r="X43" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>132.97</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>165.04</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>248.92</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>84.81999999999999</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>100.79</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>164.27</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>282.29</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>154.39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3855,6 +6082,57 @@
       <c r="W44" t="n">
         <v>108.83</v>
       </c>
+      <c r="X44" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>150.04</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>177.67</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>136.77</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>121.14</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>286.89</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>108.83</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3932,6 +6210,57 @@
       <c r="W45" t="n">
         <v>175.22</v>
       </c>
+      <c r="X45" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>189.44</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>190.35</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>242.73</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>161.49</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>171.51</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>318.29</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>175.22</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -4009,6 +6338,57 @@
       <c r="W46" t="n">
         <v>290.08</v>
       </c>
+      <c r="X46" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>220.44</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>121.73</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>283.19</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>249.76</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>132.18</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>191.98</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>290.08</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -4086,6 +6466,57 @@
       <c r="W47" t="n">
         <v>195.83</v>
       </c>
+      <c r="X47" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>122.41</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>157.76</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>131.15</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>195.83</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -4163,6 +6594,57 @@
       <c r="W48" t="n">
         <v>232.67</v>
       </c>
+      <c r="X48" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>71.69</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>257.02</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>48.51</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>108.22</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>67.20999999999999</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>129.44</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>305.75</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>232.67</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -4240,6 +6722,57 @@
       <c r="W49" t="n">
         <v>158.06</v>
       </c>
+      <c r="X49" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>109.54</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>212.72</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>155.82</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>166.29</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>158.06</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -4317,6 +6850,57 @@
       <c r="W50" t="n">
         <v>116.39</v>
       </c>
+      <c r="X50" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>96.39</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>197.75</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>107.99</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>250.84</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>116.39</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -4394,6 +6978,57 @@
       <c r="W51" t="n">
         <v>136.38</v>
       </c>
+      <c r="X51" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>278.84</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>108.03</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>154.61</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>176.28</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>169.57</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>332.15</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>136.38</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -4471,6 +7106,57 @@
       <c r="W52" t="n">
         <v>100.07</v>
       </c>
+      <c r="X52" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>193.83</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>106.28</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>153.59</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>151.81</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>73.89</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>114.82</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>180.09</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>286.21</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>100.07</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -4546,6 +7232,57 @@
         <v>294.88</v>
       </c>
       <c r="W53" t="n">
+        <v>150.07</v>
+      </c>
+      <c r="X53" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>162.01</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>135.29</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>211.85</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>195.21</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>116.82</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>168.77</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>294.88</v>
+      </c>
+      <c r="AN53" t="n">
         <v>150.07</v>
       </c>
     </row>
